--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY147"/>
+  <dimension ref="A1:AY148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7835,7 +7835,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135049001</v>
+        <v>135048983</v>
       </c>
       <c r="B64" t="n">
         <v>57975</v>
@@ -7863,25 +7863,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>657131</v>
+        <v>657203</v>
       </c>
       <c r="R64" t="n">
-        <v>7003403</v>
+        <v>7003566</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7913,7 +7925,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7923,12 +7935,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre och färska spår på tall</t>
+          <t>Trummande högst upp på en död toppbruten gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7948,14 +7960,14 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135049033</v>
+        <v>135049001</v>
       </c>
       <c r="B65" t="n">
         <v>57975</v>
@@ -7988,7 +8000,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7998,10 +8010,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>657508</v>
+        <v>657131</v>
       </c>
       <c r="R65" t="n">
-        <v>7003552</v>
+        <v>7003403</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8033,7 +8045,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8043,12 +8055,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre och färska spår på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8068,39 +8080,39 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135048974</v>
+        <v>135049033</v>
       </c>
       <c r="B66" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8108,7 +8120,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8118,10 +8130,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656894</v>
+        <v>657508</v>
       </c>
       <c r="R66" t="n">
-        <v>7003584</v>
+        <v>7003552</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8153,7 +8165,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8163,7 +8175,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8183,14 +8200,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135049022</v>
+        <v>135048974</v>
       </c>
       <c r="B67" t="n">
         <v>57162</v>
@@ -8218,37 +8235,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>657277</v>
+        <v>656894</v>
       </c>
       <c r="R67" t="n">
-        <v>7003604</v>
+        <v>7003584</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -8280,7 +8285,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8290,12 +8295,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8322,7 +8322,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135049032</v>
+        <v>135049022</v>
       </c>
       <c r="B68" t="n">
         <v>57162</v>
@@ -8355,14 +8355,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8381,10 +8377,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>657440</v>
+        <v>657277</v>
       </c>
       <c r="R68" t="n">
-        <v>7003457</v>
+        <v>7003604</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -8416,7 +8412,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8426,7 +8422,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8451,17 +8447,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135005878</v>
+        <v>135049032</v>
       </c>
       <c r="B69" t="n">
-        <v>99112</v>
+        <v>57162</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8469,21 +8465,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8491,24 +8487,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>657121</v>
+        <v>657440</v>
       </c>
       <c r="R69" t="n">
-        <v>7003635</v>
+        <v>7003457</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8537,7 +8548,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8547,7 +8558,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8562,19 +8578,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135009801</v>
+        <v>135005878</v>
       </c>
       <c r="B70" t="n">
         <v>99112</v>
@@ -8604,12 +8620,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8618,10 +8634,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>657252</v>
+        <v>657121</v>
       </c>
       <c r="R70" t="n">
-        <v>7003471</v>
+        <v>7003635</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8653,7 +8669,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8663,7 +8679,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,19 +8694,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135034742</v>
+        <v>135009801</v>
       </c>
       <c r="B71" t="n">
         <v>99112</v>
@@ -8720,12 +8736,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8733,21 +8744,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>657218</v>
+        <v>657252</v>
       </c>
       <c r="R71" t="n">
-        <v>7003557</v>
+        <v>7003471</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8776,7 +8785,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8786,7 +8795,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8795,26 +8804,25 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135048989</v>
+        <v>135034742</v>
       </c>
       <c r="B72" t="n">
         <v>99112</v>
@@ -8844,7 +8852,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8865,13 +8873,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>657281</v>
+        <v>657218</v>
       </c>
       <c r="R72" t="n">
-        <v>7003527</v>
+        <v>7003557</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8900,7 +8908,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8910,7 +8918,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8926,19 +8934,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135049031</v>
+        <v>135048989</v>
       </c>
       <c r="B73" t="n">
         <v>99112</v>
@@ -8968,7 +8976,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8989,10 +8997,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>657447</v>
+        <v>657281</v>
       </c>
       <c r="R73" t="n">
-        <v>7003498</v>
+        <v>7003527</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -9024,7 +9032,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9034,7 +9042,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9062,7 +9070,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135095195</v>
+        <v>135049031</v>
       </c>
       <c r="B74" t="n">
         <v>99112</v>
@@ -9092,7 +9100,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9113,10 +9121,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657266</v>
+        <v>657447</v>
       </c>
       <c r="R74" t="n">
-        <v>7003485</v>
+        <v>7003498</v>
       </c>
       <c r="S74" t="n">
         <v>3</v>
@@ -9148,7 +9156,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9158,7 +9166,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9174,19 +9182,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135095196</v>
+        <v>135095195</v>
       </c>
       <c r="B75" t="n">
         <v>99112</v>
@@ -9216,7 +9224,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9237,10 +9245,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657175</v>
+        <v>657266</v>
       </c>
       <c r="R75" t="n">
-        <v>7003509</v>
+        <v>7003485</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -9272,7 +9280,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9282,7 +9290,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9310,7 +9318,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135095211</v>
+        <v>135095196</v>
       </c>
       <c r="B76" t="n">
         <v>99112</v>
@@ -9340,7 +9348,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9361,10 +9369,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>657396</v>
+        <v>657175</v>
       </c>
       <c r="R76" t="n">
-        <v>7003511</v>
+        <v>7003509</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -9396,7 +9404,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9406,7 +9414,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9434,10 +9442,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119525652</v>
+        <v>135095211</v>
       </c>
       <c r="B77" t="n">
-        <v>99017</v>
+        <v>99112</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9445,37 +9453,53 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>657169</v>
+        <v>657396</v>
       </c>
       <c r="R77" t="n">
-        <v>7003646</v>
+        <v>7003511</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9499,22 +9523,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9523,28 +9547,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135002845</v>
+        <v>119525652</v>
       </c>
       <c r="B78" t="n">
-        <v>99230</v>
+        <v>99017</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9552,46 +9577,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219874</v>
+        <v>219795</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656863</v>
+        <v>657169</v>
       </c>
       <c r="R78" t="n">
-        <v>7003519</v>
+        <v>7003646</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9615,22 +9631,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9645,19 +9661,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135006904</v>
+        <v>135002845</v>
       </c>
       <c r="B79" t="n">
         <v>99230</v>
@@ -9687,7 +9703,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -9701,13 +9717,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657206</v>
+        <v>656863</v>
       </c>
       <c r="R79" t="n">
-        <v>7003602</v>
+        <v>7003519</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9736,7 +9752,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9746,7 +9762,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9773,7 +9789,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135034747</v>
+        <v>135006904</v>
       </c>
       <c r="B80" t="n">
         <v>99230</v>
@@ -9803,12 +9819,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9816,21 +9827,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>657233</v>
+        <v>657206</v>
       </c>
       <c r="R80" t="n">
-        <v>7003533</v>
+        <v>7003602</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9859,7 +9868,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9869,7 +9878,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9878,26 +9887,25 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135034758</v>
+        <v>135034747</v>
       </c>
       <c r="B81" t="n">
         <v>99230</v>
@@ -9948,10 +9956,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>657075</v>
+        <v>657233</v>
       </c>
       <c r="R81" t="n">
-        <v>7003434</v>
+        <v>7003533</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9983,7 +9991,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9993,7 +10001,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10021,7 +10029,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135034761</v>
+        <v>135034758</v>
       </c>
       <c r="B82" t="n">
         <v>99230</v>
@@ -10072,10 +10080,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657119</v>
+        <v>657075</v>
       </c>
       <c r="R82" t="n">
-        <v>7003406</v>
+        <v>7003434</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10107,7 +10115,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10117,7 +10125,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10145,7 +10153,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135034765</v>
+        <v>135034761</v>
       </c>
       <c r="B83" t="n">
         <v>99230</v>
@@ -10196,10 +10204,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657054</v>
+        <v>657119</v>
       </c>
       <c r="R83" t="n">
-        <v>7003418</v>
+        <v>7003406</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10231,7 +10239,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10241,7 +10249,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10269,7 +10277,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135048975</v>
+        <v>135034765</v>
       </c>
       <c r="B84" t="n">
         <v>99230</v>
@@ -10297,9 +10305,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -10308,13 +10328,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>656907</v>
+        <v>657054</v>
       </c>
       <c r="R84" t="n">
-        <v>7003586</v>
+        <v>7003418</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10343,7 +10363,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10353,7 +10373,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10369,19 +10389,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135049002</v>
+        <v>135048975</v>
       </c>
       <c r="B85" t="n">
         <v>99230</v>
@@ -10409,21 +10429,9 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -10432,13 +10440,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657140</v>
+        <v>656907</v>
       </c>
       <c r="R85" t="n">
-        <v>7003433</v>
+        <v>7003586</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10467,7 +10475,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10477,7 +10485,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10505,7 +10513,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135049003</v>
+        <v>135049002</v>
       </c>
       <c r="B86" t="n">
         <v>99230</v>
@@ -10535,7 +10543,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10556,10 +10564,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657136</v>
+        <v>657140</v>
       </c>
       <c r="R86" t="n">
-        <v>7003395</v>
+        <v>7003433</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10591,7 +10599,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10601,7 +10609,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10629,7 +10637,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135049023</v>
+        <v>135049003</v>
       </c>
       <c r="B87" t="n">
         <v>99230</v>
@@ -10680,10 +10688,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657346</v>
+        <v>657136</v>
       </c>
       <c r="R87" t="n">
-        <v>7003586</v>
+        <v>7003395</v>
       </c>
       <c r="S87" t="n">
         <v>3</v>
@@ -10715,7 +10723,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10725,7 +10733,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10753,7 +10761,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135049026</v>
+        <v>135049023</v>
       </c>
       <c r="B88" t="n">
         <v>99230</v>
@@ -10783,7 +10791,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10804,10 +10812,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657330</v>
+        <v>657346</v>
       </c>
       <c r="R88" t="n">
-        <v>7003554</v>
+        <v>7003586</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10839,7 +10847,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10849,7 +10857,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10877,7 +10885,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135049038</v>
+        <v>135049026</v>
       </c>
       <c r="B89" t="n">
         <v>99230</v>
@@ -10907,7 +10915,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10928,10 +10936,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>657367</v>
+        <v>657330</v>
       </c>
       <c r="R89" t="n">
-        <v>7003621</v>
+        <v>7003554</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
@@ -10963,7 +10971,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10973,7 +10981,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11001,7 +11009,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135095199</v>
+        <v>135049038</v>
       </c>
       <c r="B90" t="n">
         <v>99230</v>
@@ -11052,10 +11060,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657184</v>
+        <v>657367</v>
       </c>
       <c r="R90" t="n">
-        <v>7003549</v>
+        <v>7003621</v>
       </c>
       <c r="S90" t="n">
         <v>3</v>
@@ -11087,7 +11095,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11097,7 +11105,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11113,19 +11121,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135095202</v>
+        <v>135095199</v>
       </c>
       <c r="B91" t="n">
         <v>99230</v>
@@ -11155,7 +11163,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11176,10 +11184,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>656997</v>
+        <v>657184</v>
       </c>
       <c r="R91" t="n">
-        <v>7003415</v>
+        <v>7003549</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -11211,7 +11219,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11221,7 +11229,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11249,7 +11257,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135095204</v>
+        <v>135095202</v>
       </c>
       <c r="B92" t="n">
         <v>99230</v>
@@ -11279,7 +11287,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11300,10 +11308,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>656974</v>
+        <v>656997</v>
       </c>
       <c r="R92" t="n">
-        <v>7003505</v>
+        <v>7003415</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -11335,7 +11343,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11345,7 +11353,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11373,7 +11381,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135095206</v>
+        <v>135095204</v>
       </c>
       <c r="B93" t="n">
         <v>99230</v>
@@ -11403,7 +11411,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11424,10 +11432,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657296</v>
+        <v>656974</v>
       </c>
       <c r="R93" t="n">
-        <v>7003628</v>
+        <v>7003505</v>
       </c>
       <c r="S93" t="n">
         <v>3</v>
@@ -11459,7 +11467,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11469,7 +11477,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11497,7 +11505,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135095208</v>
+        <v>135095206</v>
       </c>
       <c r="B94" t="n">
         <v>99230</v>
@@ -11548,13 +11556,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657337</v>
+        <v>657296</v>
       </c>
       <c r="R94" t="n">
-        <v>7003545</v>
+        <v>7003628</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11583,7 +11591,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11593,7 +11601,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11621,7 +11629,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135095210</v>
+        <v>135095208</v>
       </c>
       <c r="B95" t="n">
         <v>99230</v>
@@ -11651,7 +11659,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11661,7 +11669,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -11672,10 +11680,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657249</v>
+        <v>657337</v>
       </c>
       <c r="R95" t="n">
-        <v>7003440</v>
+        <v>7003545</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11707,7 +11715,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11717,7 +11725,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11745,10 +11753,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135095207</v>
+        <v>135095210</v>
       </c>
       <c r="B96" t="n">
-        <v>111153</v>
+        <v>99230</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11756,26 +11764,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220240</v>
+        <v>219874</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11785,7 +11793,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -11796,13 +11804,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657382</v>
+        <v>657249</v>
       </c>
       <c r="R96" t="n">
-        <v>7003571</v>
+        <v>7003440</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11831,7 +11839,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11841,7 +11849,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11869,7 +11877,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135095215</v>
+        <v>135095207</v>
       </c>
       <c r="B97" t="n">
         <v>111153</v>
@@ -11899,7 +11907,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11920,10 +11928,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657442</v>
+        <v>657382</v>
       </c>
       <c r="R97" t="n">
-        <v>7003457</v>
+        <v>7003571</v>
       </c>
       <c r="S97" t="n">
         <v>3</v>
@@ -11955,7 +11963,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11965,7 +11973,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11993,52 +12001,64 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119525443</v>
+        <v>135095215</v>
       </c>
       <c r="B98" t="n">
-        <v>99118</v>
+        <v>111153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>657092</v>
+        <v>657442</v>
       </c>
       <c r="R98" t="n">
-        <v>7003598</v>
+        <v>7003457</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12062,22 +12082,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12086,28 +12106,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135048978</v>
+        <v>119525443</v>
       </c>
       <c r="B99" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12134,34 +12155,22 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657109</v>
+        <v>657092</v>
       </c>
       <c r="R99" t="n">
-        <v>7003624</v>
+        <v>7003598</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12185,22 +12194,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12209,26 +12218,25 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135048982</v>
+        <v>135048978</v>
       </c>
       <c r="B100" t="n">
         <v>99195</v>
@@ -12258,7 +12266,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12279,10 +12287,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>657247</v>
+        <v>657109</v>
       </c>
       <c r="R100" t="n">
-        <v>7003575</v>
+        <v>7003624</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -12314,7 +12322,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12324,7 +12332,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12345,55 +12353,71 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström, Vivien Renaut</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119526344</v>
+        <v>135048982</v>
       </c>
       <c r="B101" t="n">
-        <v>97989</v>
+        <v>99195</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>657297</v>
+        <v>657247</v>
       </c>
       <c r="R101" t="n">
-        <v>7003492</v>
+        <v>7003575</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12417,22 +12441,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12441,28 +12465,29 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja, Vivien Renaut, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135005564</v>
+        <v>119526344</v>
       </c>
       <c r="B102" t="n">
-        <v>98066</v>
+        <v>97989</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12487,29 +12512,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657128</v>
+        <v>657297</v>
       </c>
       <c r="R102" t="n">
-        <v>7003649</v>
+        <v>7003492</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12533,22 +12549,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12563,19 +12579,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135006022</v>
+        <v>135005564</v>
       </c>
       <c r="B103" t="n">
         <v>98066</v>
@@ -12605,7 +12621,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12619,10 +12635,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657168</v>
+        <v>657128</v>
       </c>
       <c r="R103" t="n">
-        <v>7003605</v>
+        <v>7003649</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -12654,7 +12670,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12664,7 +12680,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12691,10 +12707,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135034766</v>
+        <v>135006022</v>
       </c>
       <c r="B104" t="n">
-        <v>98054</v>
+        <v>98066</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12702,33 +12718,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221944</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>657060</v>
+        <v>657168</v>
       </c>
       <c r="R104" t="n">
-        <v>7003422</v>
+        <v>7003605</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12757,7 +12786,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12767,7 +12796,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12782,22 +12811,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135034738</v>
+        <v>135034766</v>
       </c>
       <c r="B105" t="n">
-        <v>98060</v>
+        <v>98054</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12805,23 +12834,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -12829,10 +12854,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657030</v>
+        <v>657060</v>
       </c>
       <c r="R105" t="n">
-        <v>7003559</v>
+        <v>7003422</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12864,7 +12889,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12874,7 +12899,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12901,7 +12926,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135034739</v>
+        <v>135034738</v>
       </c>
       <c r="B106" t="n">
         <v>98060</v>
@@ -12936,10 +12961,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657100</v>
+        <v>657030</v>
       </c>
       <c r="R106" t="n">
-        <v>7003617</v>
+        <v>7003559</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12971,7 +12996,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12981,7 +13006,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13008,7 +13033,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135034740</v>
+        <v>135034739</v>
       </c>
       <c r="B107" t="n">
         <v>98060</v>
@@ -13043,10 +13068,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657120</v>
+        <v>657100</v>
       </c>
       <c r="R107" t="n">
-        <v>7003623</v>
+        <v>7003617</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13078,7 +13103,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13088,7 +13113,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13115,7 +13140,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135034750</v>
+        <v>135034740</v>
       </c>
       <c r="B108" t="n">
         <v>98060</v>
@@ -13150,10 +13175,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657239</v>
+        <v>657120</v>
       </c>
       <c r="R108" t="n">
-        <v>7003455</v>
+        <v>7003623</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13185,7 +13210,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13195,7 +13220,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13222,7 +13247,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135034771</v>
+        <v>135034750</v>
       </c>
       <c r="B109" t="n">
         <v>98060</v>
@@ -13257,10 +13282,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>657383</v>
+        <v>657239</v>
       </c>
       <c r="R109" t="n">
-        <v>7003575</v>
+        <v>7003455</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13292,7 +13317,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13302,7 +13327,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13329,7 +13354,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135048973</v>
+        <v>135034771</v>
       </c>
       <c r="B110" t="n">
         <v>98060</v>
@@ -13364,13 +13389,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656898</v>
+        <v>657383</v>
       </c>
       <c r="R110" t="n">
-        <v>7003584</v>
+        <v>7003575</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13399,7 +13424,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13409,7 +13434,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13424,19 +13449,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135048987</v>
+        <v>135048973</v>
       </c>
       <c r="B111" t="n">
         <v>98060</v>
@@ -13471,10 +13496,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657260</v>
+        <v>656898</v>
       </c>
       <c r="R111" t="n">
-        <v>7003505</v>
+        <v>7003584</v>
       </c>
       <c r="S111" t="n">
         <v>3</v>
@@ -13506,7 +13531,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13516,7 +13541,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13543,7 +13568,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135049020</v>
+        <v>135048987</v>
       </c>
       <c r="B112" t="n">
         <v>98060</v>
@@ -13578,10 +13603,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657089</v>
+        <v>657260</v>
       </c>
       <c r="R112" t="n">
-        <v>7003540</v>
+        <v>7003505</v>
       </c>
       <c r="S112" t="n">
         <v>3</v>
@@ -13613,7 +13638,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13623,7 +13648,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13650,7 +13675,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135049037</v>
+        <v>135049020</v>
       </c>
       <c r="B113" t="n">
         <v>98060</v>
@@ -13685,10 +13710,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657385</v>
+        <v>657089</v>
       </c>
       <c r="R113" t="n">
-        <v>7003626</v>
+        <v>7003540</v>
       </c>
       <c r="S113" t="n">
         <v>3</v>
@@ -13720,7 +13745,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13730,7 +13755,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13757,7 +13782,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135095209</v>
+        <v>135049037</v>
       </c>
       <c r="B114" t="n">
         <v>98060</v>
@@ -13792,10 +13817,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657267</v>
+        <v>657385</v>
       </c>
       <c r="R114" t="n">
-        <v>7003445</v>
+        <v>7003626</v>
       </c>
       <c r="S114" t="n">
         <v>3</v>
@@ -13827,7 +13852,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13837,7 +13862,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13852,19 +13877,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135095212</v>
+        <v>135095209</v>
       </c>
       <c r="B115" t="n">
         <v>98060</v>
@@ -13899,10 +13924,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>657466</v>
+        <v>657267</v>
       </c>
       <c r="R115" t="n">
-        <v>7003505</v>
+        <v>7003445</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -13934,7 +13959,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13944,7 +13969,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13971,7 +13996,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135095214</v>
+        <v>135095212</v>
       </c>
       <c r="B116" t="n">
         <v>98060</v>
@@ -14006,10 +14031,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>657446</v>
+        <v>657466</v>
       </c>
       <c r="R116" t="n">
-        <v>7003461</v>
+        <v>7003505</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -14041,7 +14066,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14051,7 +14076,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14078,7 +14103,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135095219</v>
+        <v>135095214</v>
       </c>
       <c r="B117" t="n">
         <v>98060</v>
@@ -14107,27 +14132,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>657468</v>
+        <v>657446</v>
       </c>
       <c r="R117" t="n">
-        <v>7003659</v>
+        <v>7003461</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14156,7 +14173,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14166,7 +14183,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14175,7 +14192,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -14194,10 +14210,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119526215</v>
+        <v>135095219</v>
       </c>
       <c r="B118" t="n">
-        <v>99140</v>
+        <v>98060</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14205,37 +14221,45 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657282</v>
+        <v>657468</v>
       </c>
       <c r="R118" t="n">
-        <v>7003488</v>
+        <v>7003659</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14259,22 +14283,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14283,28 +14307,29 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135005577</v>
+        <v>119526215</v>
       </c>
       <c r="B119" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14329,29 +14354,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657114</v>
+        <v>657282</v>
       </c>
       <c r="R119" t="n">
-        <v>7003643</v>
+        <v>7003488</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14375,22 +14391,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14405,19 +14421,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135006961</v>
+        <v>135005577</v>
       </c>
       <c r="B120" t="n">
         <v>99217</v>
@@ -14447,12 +14463,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14461,13 +14477,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657206</v>
+        <v>657114</v>
       </c>
       <c r="R120" t="n">
-        <v>7003602</v>
+        <v>7003643</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14496,7 +14512,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14506,7 +14522,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14521,19 +14537,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135009659</v>
+        <v>135006961</v>
       </c>
       <c r="B121" t="n">
         <v>99217</v>
@@ -14563,7 +14579,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -14577,13 +14593,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657325</v>
+        <v>657206</v>
       </c>
       <c r="R121" t="n">
-        <v>7003507</v>
+        <v>7003602</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14612,7 +14628,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14622,7 +14638,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14649,7 +14665,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135009818</v>
+        <v>135009659</v>
       </c>
       <c r="B122" t="n">
         <v>99217</v>
@@ -14679,7 +14695,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -14693,13 +14709,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657252</v>
+        <v>657325</v>
       </c>
       <c r="R122" t="n">
-        <v>7003471</v>
+        <v>7003507</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14728,7 +14744,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14738,7 +14754,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14765,7 +14781,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135034755</v>
+        <v>135009818</v>
       </c>
       <c r="B123" t="n">
         <v>99217</v>
@@ -14795,12 +14811,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -14808,21 +14819,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>657206</v>
+        <v>657252</v>
       </c>
       <c r="R123" t="n">
-        <v>7003513</v>
+        <v>7003471</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14851,7 +14860,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14861,7 +14870,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14870,26 +14879,25 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135034763</v>
+        <v>135034755</v>
       </c>
       <c r="B124" t="n">
         <v>99217</v>
@@ -14919,7 +14927,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14940,10 +14948,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657128</v>
+        <v>657206</v>
       </c>
       <c r="R124" t="n">
-        <v>7003403</v>
+        <v>7003513</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14975,7 +14983,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14985,7 +14993,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15006,14 +15014,14 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135048998</v>
+        <v>135034763</v>
       </c>
       <c r="B125" t="n">
         <v>99217</v>
@@ -15043,7 +15051,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -15064,13 +15072,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657095</v>
+        <v>657128</v>
       </c>
       <c r="R125" t="n">
-        <v>7003463</v>
+        <v>7003403</v>
       </c>
       <c r="S125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15099,7 +15107,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15109,7 +15117,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15125,19 +15133,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135095194</v>
+        <v>135048998</v>
       </c>
       <c r="B126" t="n">
         <v>99217</v>
@@ -15167,7 +15175,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15188,10 +15196,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>657254</v>
+        <v>657095</v>
       </c>
       <c r="R126" t="n">
-        <v>7003424</v>
+        <v>7003463</v>
       </c>
       <c r="S126" t="n">
         <v>3</v>
@@ -15223,7 +15231,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15233,7 +15241,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15249,19 +15257,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135095213</v>
+        <v>135095194</v>
       </c>
       <c r="B127" t="n">
         <v>99217</v>
@@ -15291,7 +15299,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15312,10 +15320,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>657452</v>
+        <v>657254</v>
       </c>
       <c r="R127" t="n">
-        <v>7003460</v>
+        <v>7003424</v>
       </c>
       <c r="S127" t="n">
         <v>3</v>
@@ -15347,7 +15355,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15357,7 +15365,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15385,7 +15393,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135095221</v>
+        <v>135095213</v>
       </c>
       <c r="B128" t="n">
         <v>99217</v>
@@ -15415,7 +15423,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15436,10 +15444,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>657332</v>
+        <v>657452</v>
       </c>
       <c r="R128" t="n">
-        <v>7003626</v>
+        <v>7003460</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -15471,7 +15479,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15481,7 +15489,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15509,10 +15517,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119525842</v>
+        <v>135095221</v>
       </c>
       <c r="B129" t="n">
-        <v>101326</v>
+        <v>99217</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15520,37 +15528,53 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>657255</v>
+        <v>657332</v>
       </c>
       <c r="R129" t="n">
-        <v>7003601</v>
+        <v>7003626</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15574,22 +15598,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15598,25 +15622,26 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119525850</v>
+        <v>119525842</v>
       </c>
       <c r="B130" t="n">
         <v>101326</v>
@@ -15651,10 +15676,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>657183</v>
+        <v>657255</v>
       </c>
       <c r="R130" t="n">
-        <v>7003552</v>
+        <v>7003601</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15686,7 +15711,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15696,7 +15721,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15711,22 +15736,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135002295</v>
+        <v>119525850</v>
       </c>
       <c r="B131" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15751,24 +15776,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>656863</v>
+        <v>657183</v>
       </c>
       <c r="R131" t="n">
-        <v>7003519</v>
+        <v>7003552</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15792,22 +15813,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15822,19 +15843,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135034744</v>
+        <v>135002295</v>
       </c>
       <c r="B132" t="n">
         <v>101403</v>
@@ -15862,28 +15883,24 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>657215</v>
+        <v>656863</v>
       </c>
       <c r="R132" t="n">
-        <v>7003552</v>
+        <v>7003519</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15912,7 +15929,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15922,7 +15939,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15931,26 +15948,25 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135034752</v>
+        <v>135034744</v>
       </c>
       <c r="B133" t="n">
         <v>101403</v>
@@ -15993,10 +16009,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>657248</v>
+        <v>657215</v>
       </c>
       <c r="R133" t="n">
-        <v>7003525</v>
+        <v>7003552</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -16028,7 +16044,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16038,7 +16054,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16066,7 +16082,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135048992</v>
+        <v>135034752</v>
       </c>
       <c r="B134" t="n">
         <v>101403</v>
@@ -16096,7 +16112,11 @@
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -16105,13 +16125,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>657157</v>
+        <v>657248</v>
       </c>
       <c r="R134" t="n">
-        <v>7003506</v>
+        <v>7003525</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16140,7 +16160,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16150,7 +16170,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16166,19 +16186,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135049013</v>
+        <v>135048992</v>
       </c>
       <c r="B135" t="n">
         <v>101403</v>
@@ -16217,10 +16237,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>657033</v>
+        <v>657157</v>
       </c>
       <c r="R135" t="n">
-        <v>7003430</v>
+        <v>7003506</v>
       </c>
       <c r="S135" t="n">
         <v>3</v>
@@ -16252,7 +16272,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16262,7 +16282,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16290,7 +16310,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135049016</v>
+        <v>135049013</v>
       </c>
       <c r="B136" t="n">
         <v>101403</v>
@@ -16319,16 +16339,20 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>656992</v>
+        <v>657033</v>
       </c>
       <c r="R136" t="n">
-        <v>7003449</v>
+        <v>7003430</v>
       </c>
       <c r="S136" t="n">
         <v>3</v>
@@ -16360,7 +16384,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16370,7 +16394,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16379,6 +16403,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16397,10 +16422,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135034745</v>
+        <v>135049016</v>
       </c>
       <c r="B137" t="n">
-        <v>99472</v>
+        <v>101403</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16408,45 +16433,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>657215</v>
+        <v>656992</v>
       </c>
       <c r="R137" t="n">
-        <v>7003561</v>
+        <v>7003449</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16475,7 +16492,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16485,7 +16502,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16494,26 +16511,25 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135034757</v>
+        <v>135034745</v>
       </c>
       <c r="B138" t="n">
         <v>99472</v>
@@ -16556,10 +16572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>657142</v>
+        <v>657215</v>
       </c>
       <c r="R138" t="n">
-        <v>7003528</v>
+        <v>7003561</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16591,7 +16607,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16601,7 +16617,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16629,7 +16645,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135049012</v>
+        <v>135034757</v>
       </c>
       <c r="B139" t="n">
         <v>99472</v>
@@ -16659,7 +16675,11 @@
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -16668,13 +16688,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>657033</v>
+        <v>657142</v>
       </c>
       <c r="R139" t="n">
-        <v>7003430</v>
+        <v>7003528</v>
       </c>
       <c r="S139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16703,7 +16723,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16713,7 +16733,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16729,22 +16749,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135034746</v>
+        <v>135049012</v>
       </c>
       <c r="B140" t="n">
-        <v>99001</v>
+        <v>99472</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16752,16 +16772,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>223049</v>
+        <v>222812</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16769,21 +16789,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -16792,13 +16800,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>657249</v>
+        <v>657033</v>
       </c>
       <c r="R140" t="n">
-        <v>7003583</v>
+        <v>7003430</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16827,7 +16835,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16837,7 +16845,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16853,19 +16861,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135034759</v>
+        <v>135034746</v>
       </c>
       <c r="B141" t="n">
         <v>99001</v>
@@ -16895,7 +16903,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16916,10 +16924,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>657070</v>
+        <v>657249</v>
       </c>
       <c r="R141" t="n">
-        <v>7003439</v>
+        <v>7003583</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16951,7 +16959,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16961,7 +16969,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16989,7 +16997,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135034768</v>
+        <v>135034759</v>
       </c>
       <c r="B142" t="n">
         <v>99001</v>
@@ -17019,7 +17027,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17040,10 +17048,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>657038</v>
+        <v>657070</v>
       </c>
       <c r="R142" t="n">
-        <v>7003417</v>
+        <v>7003439</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -17075,7 +17083,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17085,7 +17093,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17113,7 +17121,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135048985</v>
+        <v>135034768</v>
       </c>
       <c r="B143" t="n">
         <v>99001</v>
@@ -17141,20 +17149,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>657214</v>
+        <v>657038</v>
       </c>
       <c r="R143" t="n">
-        <v>7003544</v>
+        <v>7003417</v>
       </c>
       <c r="S143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17183,7 +17207,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17193,7 +17217,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17202,25 +17226,26 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135048993</v>
+        <v>135048985</v>
       </c>
       <c r="B144" t="n">
         <v>99001</v>
@@ -17255,10 +17280,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>657170</v>
+        <v>657214</v>
       </c>
       <c r="R144" t="n">
-        <v>7003517</v>
+        <v>7003544</v>
       </c>
       <c r="S144" t="n">
         <v>3</v>
@@ -17290,7 +17315,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17300,7 +17325,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17327,7 +17352,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135049010</v>
+        <v>135048993</v>
       </c>
       <c r="B145" t="n">
         <v>99001</v>
@@ -17355,33 +17380,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>657039</v>
+        <v>657170</v>
       </c>
       <c r="R145" t="n">
-        <v>7003436</v>
+        <v>7003517</v>
       </c>
       <c r="S145" t="n">
         <v>3</v>
@@ -17413,7 +17422,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17423,7 +17432,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17432,7 +17441,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -17451,7 +17459,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135095201</v>
+        <v>135049010</v>
       </c>
       <c r="B146" t="n">
         <v>99001</v>
@@ -17481,7 +17489,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17502,10 +17510,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>656998</v>
+        <v>657039</v>
       </c>
       <c r="R146" t="n">
-        <v>7003420</v>
+        <v>7003436</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -17537,7 +17545,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17547,7 +17555,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17563,19 +17571,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135095203</v>
+        <v>135095201</v>
       </c>
       <c r="B147" t="n">
         <v>99001</v>
@@ -17605,7 +17613,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17626,10 +17634,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>656997</v>
+        <v>656998</v>
       </c>
       <c r="R147" t="n">
-        <v>7003424</v>
+        <v>7003420</v>
       </c>
       <c r="S147" t="n">
         <v>3</v>
@@ -17661,7 +17669,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17671,7 +17679,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17696,6 +17704,130 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>135095203</v>
+      </c>
+      <c r="B148" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Lomtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>656997</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7003424</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AY149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8080,14 +8080,14 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135049033</v>
+        <v>135049028</v>
       </c>
       <c r="B66" t="n">
         <v>57975</v>
@@ -8120,7 +8120,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8130,13 +8130,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>657508</v>
+        <v>657326</v>
       </c>
       <c r="R66" t="n">
-        <v>7003552</v>
+        <v>7003550</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8175,19 +8175,19 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Bohål 4,5 cm ingångsdiameter, ca 3 meter upp på en asp och i lämplig biotop för arten. Sannolikt tillhörande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -8200,39 +8200,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135048974</v>
+        <v>135049033</v>
       </c>
       <c r="B67" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8240,7 +8240,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656894</v>
+        <v>657508</v>
       </c>
       <c r="R67" t="n">
-        <v>7003584</v>
+        <v>7003552</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8295,7 +8295,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8315,14 +8320,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135049022</v>
+        <v>135048974</v>
       </c>
       <c r="B68" t="n">
         <v>57162</v>
@@ -8350,37 +8355,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>657277</v>
+        <v>656894</v>
       </c>
       <c r="R68" t="n">
-        <v>7003604</v>
+        <v>7003584</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -8412,7 +8405,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8422,12 +8415,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,7 +8442,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135049032</v>
+        <v>135049022</v>
       </c>
       <c r="B69" t="n">
         <v>57162</v>
@@ -8487,14 +8475,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8513,10 +8497,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>657440</v>
+        <v>657277</v>
       </c>
       <c r="R69" t="n">
-        <v>7003457</v>
+        <v>7003604</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -8548,7 +8532,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8558,7 +8542,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8583,17 +8567,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135005878</v>
+        <v>135049032</v>
       </c>
       <c r="B70" t="n">
-        <v>99112</v>
+        <v>57162</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8601,21 +8585,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8623,24 +8607,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>657121</v>
+        <v>657440</v>
       </c>
       <c r="R70" t="n">
-        <v>7003635</v>
+        <v>7003457</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8669,7 +8668,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8679,7 +8678,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8694,19 +8698,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135009801</v>
+        <v>135005878</v>
       </c>
       <c r="B71" t="n">
         <v>99112</v>
@@ -8736,12 +8740,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8750,10 +8754,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>657252</v>
+        <v>657121</v>
       </c>
       <c r="R71" t="n">
-        <v>7003471</v>
+        <v>7003635</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8785,7 +8789,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8795,7 +8799,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8810,19 +8814,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135034742</v>
+        <v>135009801</v>
       </c>
       <c r="B72" t="n">
         <v>99112</v>
@@ -8852,12 +8856,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8865,21 +8864,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>657218</v>
+        <v>657252</v>
       </c>
       <c r="R72" t="n">
-        <v>7003557</v>
+        <v>7003471</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8908,7 +8905,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8918,7 +8915,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8927,26 +8924,25 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135048989</v>
+        <v>135034742</v>
       </c>
       <c r="B73" t="n">
         <v>99112</v>
@@ -8976,7 +8972,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8997,13 +8993,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>657281</v>
+        <v>657218</v>
       </c>
       <c r="R73" t="n">
-        <v>7003527</v>
+        <v>7003557</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9032,7 +9028,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9042,7 +9038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9058,19 +9054,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135049031</v>
+        <v>135048989</v>
       </c>
       <c r="B74" t="n">
         <v>99112</v>
@@ -9100,7 +9096,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9121,10 +9117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657447</v>
+        <v>657281</v>
       </c>
       <c r="R74" t="n">
-        <v>7003498</v>
+        <v>7003527</v>
       </c>
       <c r="S74" t="n">
         <v>3</v>
@@ -9156,7 +9152,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9166,7 +9162,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9194,7 +9190,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135095195</v>
+        <v>135049031</v>
       </c>
       <c r="B75" t="n">
         <v>99112</v>
@@ -9224,7 +9220,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9245,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657266</v>
+        <v>657447</v>
       </c>
       <c r="R75" t="n">
-        <v>7003485</v>
+        <v>7003498</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -9280,7 +9276,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9290,7 +9286,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9306,19 +9302,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135095196</v>
+        <v>135095195</v>
       </c>
       <c r="B76" t="n">
         <v>99112</v>
@@ -9348,7 +9344,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9369,10 +9365,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>657175</v>
+        <v>657266</v>
       </c>
       <c r="R76" t="n">
-        <v>7003509</v>
+        <v>7003485</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -9404,7 +9400,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9414,7 +9410,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9442,7 +9438,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135095211</v>
+        <v>135095196</v>
       </c>
       <c r="B77" t="n">
         <v>99112</v>
@@ -9472,7 +9468,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9493,10 +9489,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>657396</v>
+        <v>657175</v>
       </c>
       <c r="R77" t="n">
-        <v>7003511</v>
+        <v>7003509</v>
       </c>
       <c r="S77" t="n">
         <v>3</v>
@@ -9528,7 +9524,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9538,7 +9534,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9566,10 +9562,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119525652</v>
+        <v>135095211</v>
       </c>
       <c r="B78" t="n">
-        <v>99017</v>
+        <v>99112</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,37 +9573,53 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657169</v>
+        <v>657396</v>
       </c>
       <c r="R78" t="n">
-        <v>7003646</v>
+        <v>7003511</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9631,22 +9643,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9655,28 +9667,29 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135002845</v>
+        <v>119525652</v>
       </c>
       <c r="B79" t="n">
-        <v>99230</v>
+        <v>99017</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9684,46 +9697,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219874</v>
+        <v>219795</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656863</v>
+        <v>657169</v>
       </c>
       <c r="R79" t="n">
-        <v>7003519</v>
+        <v>7003646</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9747,22 +9751,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9777,19 +9781,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135006904</v>
+        <v>135002845</v>
       </c>
       <c r="B80" t="n">
         <v>99230</v>
@@ -9819,7 +9823,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9833,13 +9837,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>657206</v>
+        <v>656863</v>
       </c>
       <c r="R80" t="n">
-        <v>7003602</v>
+        <v>7003519</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9868,7 +9872,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9878,7 +9882,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9905,7 +9909,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135034747</v>
+        <v>135006904</v>
       </c>
       <c r="B81" t="n">
         <v>99230</v>
@@ -9935,12 +9939,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -9948,21 +9947,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>657233</v>
+        <v>657206</v>
       </c>
       <c r="R81" t="n">
-        <v>7003533</v>
+        <v>7003602</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9991,7 +9988,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10001,7 +9998,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10010,26 +10007,25 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135034758</v>
+        <v>135034747</v>
       </c>
       <c r="B82" t="n">
         <v>99230</v>
@@ -10080,10 +10076,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657075</v>
+        <v>657233</v>
       </c>
       <c r="R82" t="n">
-        <v>7003434</v>
+        <v>7003533</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10115,7 +10111,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10125,7 +10121,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10153,7 +10149,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135034761</v>
+        <v>135034758</v>
       </c>
       <c r="B83" t="n">
         <v>99230</v>
@@ -10204,10 +10200,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657119</v>
+        <v>657075</v>
       </c>
       <c r="R83" t="n">
-        <v>7003406</v>
+        <v>7003434</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10239,7 +10235,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10249,7 +10245,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10277,7 +10273,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135034765</v>
+        <v>135034761</v>
       </c>
       <c r="B84" t="n">
         <v>99230</v>
@@ -10328,10 +10324,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>657054</v>
+        <v>657119</v>
       </c>
       <c r="R84" t="n">
-        <v>7003418</v>
+        <v>7003406</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10363,7 +10359,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10373,7 +10369,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10401,7 +10397,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135048975</v>
+        <v>135034765</v>
       </c>
       <c r="B85" t="n">
         <v>99230</v>
@@ -10429,9 +10425,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -10440,13 +10448,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>656907</v>
+        <v>657054</v>
       </c>
       <c r="R85" t="n">
-        <v>7003586</v>
+        <v>7003418</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10475,7 +10483,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10485,7 +10493,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10501,19 +10509,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135049002</v>
+        <v>135048975</v>
       </c>
       <c r="B86" t="n">
         <v>99230</v>
@@ -10541,21 +10549,9 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -10564,13 +10560,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657140</v>
+        <v>656907</v>
       </c>
       <c r="R86" t="n">
-        <v>7003433</v>
+        <v>7003586</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10599,7 +10595,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10609,7 +10605,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10637,7 +10633,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135049003</v>
+        <v>135049002</v>
       </c>
       <c r="B87" t="n">
         <v>99230</v>
@@ -10667,7 +10663,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10688,10 +10684,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657136</v>
+        <v>657140</v>
       </c>
       <c r="R87" t="n">
-        <v>7003395</v>
+        <v>7003433</v>
       </c>
       <c r="S87" t="n">
         <v>3</v>
@@ -10723,7 +10719,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10733,7 +10729,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10761,7 +10757,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135049023</v>
+        <v>135049003</v>
       </c>
       <c r="B88" t="n">
         <v>99230</v>
@@ -10812,10 +10808,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657346</v>
+        <v>657136</v>
       </c>
       <c r="R88" t="n">
-        <v>7003586</v>
+        <v>7003395</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10847,7 +10843,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10857,7 +10853,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10885,7 +10881,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135049026</v>
+        <v>135049023</v>
       </c>
       <c r="B89" t="n">
         <v>99230</v>
@@ -10915,7 +10911,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10936,10 +10932,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>657330</v>
+        <v>657346</v>
       </c>
       <c r="R89" t="n">
-        <v>7003554</v>
+        <v>7003586</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
@@ -10971,7 +10967,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10981,7 +10977,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11009,7 +11005,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135049038</v>
+        <v>135049026</v>
       </c>
       <c r="B90" t="n">
         <v>99230</v>
@@ -11039,7 +11035,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11060,10 +11056,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657367</v>
+        <v>657330</v>
       </c>
       <c r="R90" t="n">
-        <v>7003621</v>
+        <v>7003554</v>
       </c>
       <c r="S90" t="n">
         <v>3</v>
@@ -11095,7 +11091,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11105,7 +11101,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11133,7 +11129,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135095199</v>
+        <v>135049038</v>
       </c>
       <c r="B91" t="n">
         <v>99230</v>
@@ -11184,10 +11180,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657184</v>
+        <v>657367</v>
       </c>
       <c r="R91" t="n">
-        <v>7003549</v>
+        <v>7003621</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -11219,7 +11215,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11229,7 +11225,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11245,19 +11241,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135095202</v>
+        <v>135095199</v>
       </c>
       <c r="B92" t="n">
         <v>99230</v>
@@ -11287,7 +11283,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11308,10 +11304,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>656997</v>
+        <v>657184</v>
       </c>
       <c r="R92" t="n">
-        <v>7003415</v>
+        <v>7003549</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -11343,7 +11339,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11353,7 +11349,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11381,7 +11377,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135095204</v>
+        <v>135095202</v>
       </c>
       <c r="B93" t="n">
         <v>99230</v>
@@ -11411,7 +11407,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11432,10 +11428,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>656974</v>
+        <v>656997</v>
       </c>
       <c r="R93" t="n">
-        <v>7003505</v>
+        <v>7003415</v>
       </c>
       <c r="S93" t="n">
         <v>3</v>
@@ -11467,7 +11463,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11477,7 +11473,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11505,7 +11501,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135095206</v>
+        <v>135095204</v>
       </c>
       <c r="B94" t="n">
         <v>99230</v>
@@ -11535,7 +11531,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11556,10 +11552,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657296</v>
+        <v>656974</v>
       </c>
       <c r="R94" t="n">
-        <v>7003628</v>
+        <v>7003505</v>
       </c>
       <c r="S94" t="n">
         <v>3</v>
@@ -11591,7 +11587,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11601,7 +11597,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11629,7 +11625,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135095208</v>
+        <v>135095206</v>
       </c>
       <c r="B95" t="n">
         <v>99230</v>
@@ -11680,13 +11676,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657337</v>
+        <v>657296</v>
       </c>
       <c r="R95" t="n">
-        <v>7003545</v>
+        <v>7003628</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11715,7 +11711,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11725,7 +11721,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11753,7 +11749,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135095210</v>
+        <v>135095208</v>
       </c>
       <c r="B96" t="n">
         <v>99230</v>
@@ -11783,7 +11779,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11793,7 +11789,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -11804,10 +11800,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657249</v>
+        <v>657337</v>
       </c>
       <c r="R96" t="n">
-        <v>7003440</v>
+        <v>7003545</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -11839,7 +11835,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11849,7 +11845,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11877,10 +11873,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135095207</v>
+        <v>135095210</v>
       </c>
       <c r="B97" t="n">
-        <v>111153</v>
+        <v>99230</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11888,26 +11884,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220240</v>
+        <v>219874</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11917,7 +11913,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -11928,13 +11924,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657382</v>
+        <v>657249</v>
       </c>
       <c r="R97" t="n">
-        <v>7003571</v>
+        <v>7003440</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11963,7 +11959,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11973,7 +11969,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12001,7 +11997,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135095215</v>
+        <v>135095207</v>
       </c>
       <c r="B98" t="n">
         <v>111153</v>
@@ -12031,7 +12027,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12052,10 +12048,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>657442</v>
+        <v>657382</v>
       </c>
       <c r="R98" t="n">
-        <v>7003457</v>
+        <v>7003571</v>
       </c>
       <c r="S98" t="n">
         <v>3</v>
@@ -12087,7 +12083,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12097,7 +12093,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12125,52 +12121,64 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119525443</v>
+        <v>135095215</v>
       </c>
       <c r="B99" t="n">
-        <v>99118</v>
+        <v>111153</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657092</v>
+        <v>657442</v>
       </c>
       <c r="R99" t="n">
-        <v>7003598</v>
+        <v>7003457</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12194,22 +12202,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12218,28 +12226,29 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135048978</v>
+        <v>119525443</v>
       </c>
       <c r="B100" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12266,34 +12275,22 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>657109</v>
+        <v>657092</v>
       </c>
       <c r="R100" t="n">
-        <v>7003624</v>
+        <v>7003598</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12317,22 +12314,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12341,26 +12338,25 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135048982</v>
+        <v>135048978</v>
       </c>
       <c r="B101" t="n">
         <v>99195</v>
@@ -12390,7 +12386,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12411,10 +12407,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>657247</v>
+        <v>657109</v>
       </c>
       <c r="R101" t="n">
-        <v>7003575</v>
+        <v>7003624</v>
       </c>
       <c r="S101" t="n">
         <v>3</v>
@@ -12446,7 +12442,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12456,7 +12452,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12477,55 +12473,71 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119526344</v>
+        <v>135048982</v>
       </c>
       <c r="B102" t="n">
-        <v>97989</v>
+        <v>99195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657297</v>
+        <v>657247</v>
       </c>
       <c r="R102" t="n">
-        <v>7003492</v>
+        <v>7003575</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12549,22 +12561,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12573,28 +12585,29 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135005564</v>
+        <v>119526344</v>
       </c>
       <c r="B103" t="n">
-        <v>98066</v>
+        <v>97989</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12619,29 +12632,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657128</v>
+        <v>657297</v>
       </c>
       <c r="R103" t="n">
-        <v>7003649</v>
+        <v>7003492</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12665,22 +12669,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12695,19 +12699,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135006022</v>
+        <v>135005564</v>
       </c>
       <c r="B104" t="n">
         <v>98066</v>
@@ -12737,7 +12741,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12751,10 +12755,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>657168</v>
+        <v>657128</v>
       </c>
       <c r="R104" t="n">
-        <v>7003605</v>
+        <v>7003649</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -12786,7 +12790,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12796,7 +12800,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12823,10 +12827,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135034766</v>
+        <v>135006022</v>
       </c>
       <c r="B105" t="n">
-        <v>98054</v>
+        <v>98066</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12834,33 +12838,46 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221944</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657060</v>
+        <v>657168</v>
       </c>
       <c r="R105" t="n">
-        <v>7003422</v>
+        <v>7003605</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12889,7 +12906,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12899,7 +12916,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12914,22 +12931,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135034738</v>
+        <v>135034766</v>
       </c>
       <c r="B106" t="n">
-        <v>98060</v>
+        <v>98054</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12937,23 +12954,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12961,10 +12974,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657030</v>
+        <v>657060</v>
       </c>
       <c r="R106" t="n">
-        <v>7003559</v>
+        <v>7003422</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12996,7 +13009,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13006,7 +13019,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13033,7 +13046,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135034739</v>
+        <v>135034738</v>
       </c>
       <c r="B107" t="n">
         <v>98060</v>
@@ -13068,10 +13081,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657100</v>
+        <v>657030</v>
       </c>
       <c r="R107" t="n">
-        <v>7003617</v>
+        <v>7003559</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13103,7 +13116,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13113,7 +13126,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13140,7 +13153,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135034740</v>
+        <v>135034739</v>
       </c>
       <c r="B108" t="n">
         <v>98060</v>
@@ -13175,10 +13188,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657120</v>
+        <v>657100</v>
       </c>
       <c r="R108" t="n">
-        <v>7003623</v>
+        <v>7003617</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13210,7 +13223,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13220,7 +13233,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13247,7 +13260,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135034750</v>
+        <v>135034740</v>
       </c>
       <c r="B109" t="n">
         <v>98060</v>
@@ -13282,10 +13295,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>657239</v>
+        <v>657120</v>
       </c>
       <c r="R109" t="n">
-        <v>7003455</v>
+        <v>7003623</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13317,7 +13330,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13327,7 +13340,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13354,7 +13367,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135034771</v>
+        <v>135034750</v>
       </c>
       <c r="B110" t="n">
         <v>98060</v>
@@ -13389,10 +13402,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>657383</v>
+        <v>657239</v>
       </c>
       <c r="R110" t="n">
-        <v>7003575</v>
+        <v>7003455</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13424,7 +13437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13434,7 +13447,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13461,7 +13474,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135048973</v>
+        <v>135034771</v>
       </c>
       <c r="B111" t="n">
         <v>98060</v>
@@ -13496,13 +13509,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>656898</v>
+        <v>657383</v>
       </c>
       <c r="R111" t="n">
-        <v>7003584</v>
+        <v>7003575</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13531,7 +13544,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13541,7 +13554,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13556,19 +13569,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135048987</v>
+        <v>135048973</v>
       </c>
       <c r="B112" t="n">
         <v>98060</v>
@@ -13603,10 +13616,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657260</v>
+        <v>656898</v>
       </c>
       <c r="R112" t="n">
-        <v>7003505</v>
+        <v>7003584</v>
       </c>
       <c r="S112" t="n">
         <v>3</v>
@@ -13638,7 +13651,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13648,7 +13661,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13675,7 +13688,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135049020</v>
+        <v>135048987</v>
       </c>
       <c r="B113" t="n">
         <v>98060</v>
@@ -13710,10 +13723,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657089</v>
+        <v>657260</v>
       </c>
       <c r="R113" t="n">
-        <v>7003540</v>
+        <v>7003505</v>
       </c>
       <c r="S113" t="n">
         <v>3</v>
@@ -13745,7 +13758,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13755,7 +13768,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13782,7 +13795,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135049037</v>
+        <v>135049020</v>
       </c>
       <c r="B114" t="n">
         <v>98060</v>
@@ -13817,10 +13830,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657385</v>
+        <v>657089</v>
       </c>
       <c r="R114" t="n">
-        <v>7003626</v>
+        <v>7003540</v>
       </c>
       <c r="S114" t="n">
         <v>3</v>
@@ -13852,7 +13865,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13862,7 +13875,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13889,7 +13902,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135095209</v>
+        <v>135049037</v>
       </c>
       <c r="B115" t="n">
         <v>98060</v>
@@ -13924,10 +13937,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>657267</v>
+        <v>657385</v>
       </c>
       <c r="R115" t="n">
-        <v>7003445</v>
+        <v>7003626</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -13959,7 +13972,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13969,7 +13982,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13984,19 +13997,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135095212</v>
+        <v>135095209</v>
       </c>
       <c r="B116" t="n">
         <v>98060</v>
@@ -14031,10 +14044,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>657466</v>
+        <v>657267</v>
       </c>
       <c r="R116" t="n">
-        <v>7003505</v>
+        <v>7003445</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -14066,7 +14079,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14076,7 +14089,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14103,7 +14116,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135095214</v>
+        <v>135095212</v>
       </c>
       <c r="B117" t="n">
         <v>98060</v>
@@ -14138,10 +14151,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>657446</v>
+        <v>657466</v>
       </c>
       <c r="R117" t="n">
-        <v>7003461</v>
+        <v>7003505</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -14173,7 +14186,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14183,7 +14196,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14210,7 +14223,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135095219</v>
+        <v>135095214</v>
       </c>
       <c r="B118" t="n">
         <v>98060</v>
@@ -14239,27 +14252,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657468</v>
+        <v>657446</v>
       </c>
       <c r="R118" t="n">
-        <v>7003659</v>
+        <v>7003461</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14288,7 +14293,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14298,7 +14303,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14307,7 +14312,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -14326,10 +14330,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119526215</v>
+        <v>135095219</v>
       </c>
       <c r="B119" t="n">
-        <v>99140</v>
+        <v>98060</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14337,37 +14341,45 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657282</v>
+        <v>657468</v>
       </c>
       <c r="R119" t="n">
-        <v>7003488</v>
+        <v>7003659</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14391,22 +14403,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14415,28 +14427,29 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135005577</v>
+        <v>119526215</v>
       </c>
       <c r="B120" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14461,29 +14474,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657114</v>
+        <v>657282</v>
       </c>
       <c r="R120" t="n">
-        <v>7003643</v>
+        <v>7003488</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14507,22 +14511,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14537,19 +14541,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Maria Hedenström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135006961</v>
+        <v>135005577</v>
       </c>
       <c r="B121" t="n">
         <v>99217</v>
@@ -14579,12 +14583,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14593,13 +14597,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657206</v>
+        <v>657114</v>
       </c>
       <c r="R121" t="n">
-        <v>7003602</v>
+        <v>7003643</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14628,7 +14632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14638,7 +14642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14653,19 +14657,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Maria Hedenström</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135009659</v>
+        <v>135006961</v>
       </c>
       <c r="B122" t="n">
         <v>99217</v>
@@ -14695,7 +14699,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -14709,13 +14713,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657325</v>
+        <v>657206</v>
       </c>
       <c r="R122" t="n">
-        <v>7003507</v>
+        <v>7003602</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14744,7 +14748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14754,7 +14758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14781,7 +14785,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135009818</v>
+        <v>135009659</v>
       </c>
       <c r="B123" t="n">
         <v>99217</v>
@@ -14811,7 +14815,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -14825,13 +14829,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>657252</v>
+        <v>657325</v>
       </c>
       <c r="R123" t="n">
-        <v>7003471</v>
+        <v>7003507</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14860,7 +14864,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14870,7 +14874,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14897,7 +14901,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135034755</v>
+        <v>135009818</v>
       </c>
       <c r="B124" t="n">
         <v>99217</v>
@@ -14927,12 +14931,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -14940,21 +14939,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657206</v>
+        <v>657252</v>
       </c>
       <c r="R124" t="n">
-        <v>7003513</v>
+        <v>7003471</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14983,7 +14980,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14993,7 +14990,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15002,26 +14999,25 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135034763</v>
+        <v>135034755</v>
       </c>
       <c r="B125" t="n">
         <v>99217</v>
@@ -15051,7 +15047,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -15072,10 +15068,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657128</v>
+        <v>657206</v>
       </c>
       <c r="R125" t="n">
-        <v>7003403</v>
+        <v>7003513</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15107,7 +15103,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15117,7 +15113,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15138,14 +15134,14 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135048998</v>
+        <v>135034763</v>
       </c>
       <c r="B126" t="n">
         <v>99217</v>
@@ -15175,7 +15171,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15196,13 +15192,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>657095</v>
+        <v>657128</v>
       </c>
       <c r="R126" t="n">
-        <v>7003463</v>
+        <v>7003403</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15231,7 +15227,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15241,7 +15237,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15257,19 +15253,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135095194</v>
+        <v>135048998</v>
       </c>
       <c r="B127" t="n">
         <v>99217</v>
@@ -15299,7 +15295,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15320,10 +15316,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>657254</v>
+        <v>657095</v>
       </c>
       <c r="R127" t="n">
-        <v>7003424</v>
+        <v>7003463</v>
       </c>
       <c r="S127" t="n">
         <v>3</v>
@@ -15355,7 +15351,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15365,7 +15361,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15381,19 +15377,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135095213</v>
+        <v>135095194</v>
       </c>
       <c r="B128" t="n">
         <v>99217</v>
@@ -15423,7 +15419,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15444,10 +15440,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>657452</v>
+        <v>657254</v>
       </c>
       <c r="R128" t="n">
-        <v>7003460</v>
+        <v>7003424</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -15479,7 +15475,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15489,7 +15485,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15517,7 +15513,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135095221</v>
+        <v>135095213</v>
       </c>
       <c r="B129" t="n">
         <v>99217</v>
@@ -15547,7 +15543,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15568,10 +15564,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>657332</v>
+        <v>657452</v>
       </c>
       <c r="R129" t="n">
-        <v>7003626</v>
+        <v>7003460</v>
       </c>
       <c r="S129" t="n">
         <v>3</v>
@@ -15603,7 +15599,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15613,7 +15609,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15641,10 +15637,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119525842</v>
+        <v>135095221</v>
       </c>
       <c r="B130" t="n">
-        <v>101326</v>
+        <v>99217</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15652,37 +15648,53 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>657255</v>
+        <v>657332</v>
       </c>
       <c r="R130" t="n">
-        <v>7003601</v>
+        <v>7003626</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15706,22 +15718,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15730,25 +15742,26 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119525850</v>
+        <v>119525842</v>
       </c>
       <c r="B131" t="n">
         <v>101326</v>
@@ -15783,10 +15796,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>657183</v>
+        <v>657255</v>
       </c>
       <c r="R131" t="n">
-        <v>7003552</v>
+        <v>7003601</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15818,7 +15831,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15828,7 +15841,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15843,22 +15856,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135002295</v>
+        <v>119525850</v>
       </c>
       <c r="B132" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15883,24 +15896,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>656863</v>
+        <v>657183</v>
       </c>
       <c r="R132" t="n">
-        <v>7003519</v>
+        <v>7003552</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15924,22 +15933,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15954,19 +15963,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135034744</v>
+        <v>135002295</v>
       </c>
       <c r="B133" t="n">
         <v>101403</v>
@@ -15994,28 +16003,24 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>657215</v>
+        <v>656863</v>
       </c>
       <c r="R133" t="n">
-        <v>7003552</v>
+        <v>7003519</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16044,7 +16049,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16054,7 +16059,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16063,26 +16068,25 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135034752</v>
+        <v>135034744</v>
       </c>
       <c r="B134" t="n">
         <v>101403</v>
@@ -16125,10 +16129,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>657248</v>
+        <v>657215</v>
       </c>
       <c r="R134" t="n">
-        <v>7003525</v>
+        <v>7003552</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16160,7 +16164,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16170,7 +16174,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16198,7 +16202,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135048992</v>
+        <v>135034752</v>
       </c>
       <c r="B135" t="n">
         <v>101403</v>
@@ -16228,7 +16232,11 @@
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -16237,13 +16245,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>657157</v>
+        <v>657248</v>
       </c>
       <c r="R135" t="n">
-        <v>7003506</v>
+        <v>7003525</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16272,7 +16280,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16282,7 +16290,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16298,19 +16306,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135049013</v>
+        <v>135048992</v>
       </c>
       <c r="B136" t="n">
         <v>101403</v>
@@ -16349,10 +16357,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>657033</v>
+        <v>657157</v>
       </c>
       <c r="R136" t="n">
-        <v>7003430</v>
+        <v>7003506</v>
       </c>
       <c r="S136" t="n">
         <v>3</v>
@@ -16384,7 +16392,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16394,7 +16402,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16422,7 +16430,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135049016</v>
+        <v>135049013</v>
       </c>
       <c r="B137" t="n">
         <v>101403</v>
@@ -16451,16 +16459,20 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>656992</v>
+        <v>657033</v>
       </c>
       <c r="R137" t="n">
-        <v>7003449</v>
+        <v>7003430</v>
       </c>
       <c r="S137" t="n">
         <v>3</v>
@@ -16492,7 +16504,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16502,7 +16514,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16511,6 +16523,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16529,10 +16542,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135034745</v>
+        <v>135049016</v>
       </c>
       <c r="B138" t="n">
-        <v>99472</v>
+        <v>101403</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16540,45 +16553,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>657215</v>
+        <v>656992</v>
       </c>
       <c r="R138" t="n">
-        <v>7003561</v>
+        <v>7003449</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16607,7 +16612,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16617,7 +16622,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16626,26 +16631,25 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135034757</v>
+        <v>135034745</v>
       </c>
       <c r="B139" t="n">
         <v>99472</v>
@@ -16688,10 +16692,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>657142</v>
+        <v>657215</v>
       </c>
       <c r="R139" t="n">
-        <v>7003528</v>
+        <v>7003561</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16723,7 +16727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16733,7 +16737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16761,7 +16765,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135049012</v>
+        <v>135034757</v>
       </c>
       <c r="B140" t="n">
         <v>99472</v>
@@ -16791,7 +16795,11 @@
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -16800,13 +16808,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>657033</v>
+        <v>657142</v>
       </c>
       <c r="R140" t="n">
-        <v>7003430</v>
+        <v>7003528</v>
       </c>
       <c r="S140" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16835,7 +16843,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16845,7 +16853,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16861,22 +16869,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135034746</v>
+        <v>135049012</v>
       </c>
       <c r="B141" t="n">
-        <v>99001</v>
+        <v>99472</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16884,16 +16892,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>223049</v>
+        <v>222812</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -16901,21 +16909,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -16924,13 +16920,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>657249</v>
+        <v>657033</v>
       </c>
       <c r="R141" t="n">
-        <v>7003583</v>
+        <v>7003430</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16959,7 +16955,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16969,7 +16965,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16985,19 +16981,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135034759</v>
+        <v>135034746</v>
       </c>
       <c r="B142" t="n">
         <v>99001</v>
@@ -17027,7 +17023,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17048,10 +17044,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>657070</v>
+        <v>657249</v>
       </c>
       <c r="R142" t="n">
-        <v>7003439</v>
+        <v>7003583</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -17083,7 +17079,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17093,7 +17089,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17121,7 +17117,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135034768</v>
+        <v>135034759</v>
       </c>
       <c r="B143" t="n">
         <v>99001</v>
@@ -17151,7 +17147,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17172,10 +17168,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>657038</v>
+        <v>657070</v>
       </c>
       <c r="R143" t="n">
-        <v>7003417</v>
+        <v>7003439</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17207,7 +17203,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17217,7 +17213,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17245,7 +17241,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135048985</v>
+        <v>135034768</v>
       </c>
       <c r="B144" t="n">
         <v>99001</v>
@@ -17273,20 +17269,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>657214</v>
+        <v>657038</v>
       </c>
       <c r="R144" t="n">
-        <v>7003544</v>
+        <v>7003417</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17315,7 +17327,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17325,7 +17337,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17334,25 +17346,26 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135048993</v>
+        <v>135048985</v>
       </c>
       <c r="B145" t="n">
         <v>99001</v>
@@ -17387,10 +17400,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>657170</v>
+        <v>657214</v>
       </c>
       <c r="R145" t="n">
-        <v>7003517</v>
+        <v>7003544</v>
       </c>
       <c r="S145" t="n">
         <v>3</v>
@@ -17422,7 +17435,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17432,7 +17445,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17459,7 +17472,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135049010</v>
+        <v>135048993</v>
       </c>
       <c r="B146" t="n">
         <v>99001</v>
@@ -17487,33 +17500,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>657039</v>
+        <v>657170</v>
       </c>
       <c r="R146" t="n">
-        <v>7003436</v>
+        <v>7003517</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -17545,7 +17542,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17555,7 +17552,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17564,7 +17561,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -17583,7 +17579,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135095201</v>
+        <v>135049010</v>
       </c>
       <c r="B147" t="n">
         <v>99001</v>
@@ -17613,7 +17609,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17634,10 +17630,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>656998</v>
+        <v>657039</v>
       </c>
       <c r="R147" t="n">
-        <v>7003420</v>
+        <v>7003436</v>
       </c>
       <c r="S147" t="n">
         <v>3</v>
@@ -17669,7 +17665,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17679,7 +17675,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17695,19 +17691,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135095203</v>
+        <v>135095201</v>
       </c>
       <c r="B148" t="n">
         <v>99001</v>
@@ -17737,7 +17733,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17758,10 +17754,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>656997</v>
+        <v>656998</v>
       </c>
       <c r="R148" t="n">
-        <v>7003424</v>
+        <v>7003420</v>
       </c>
       <c r="S148" t="n">
         <v>3</v>
@@ -17793,7 +17789,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17803,7 +17799,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17828,6 +17824,130 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>135095203</v>
+      </c>
+      <c r="B149" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Lomtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>656997</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7003424</v>
+      </c>
+      <c r="S149" t="n">
+        <v>3</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY149"/>
+  <dimension ref="A1:AZ149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526406</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048972</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049024</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034751</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049006</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049029</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048969</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095197</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095200</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095218</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528534</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034733</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034734</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2536,6 +2621,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034735</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048979</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2769,6 +2864,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049004</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2895,6 +2995,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049036</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3002,6 +3107,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095216</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3109,6 +3219,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095217</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3216,6 +3331,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048999</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3342,6 +3462,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049015</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3468,6 +3593,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049034</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3594,6 +3724,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048976</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3720,6 +3855,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048977</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3846,6 +3986,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048980</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3953,6 +4098,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048984</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4079,6 +4229,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048988</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4205,6 +4360,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048990</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4312,6 +4472,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048991</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4438,6 +4603,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048994</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4545,6 +4715,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048997</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4671,6 +4846,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049000</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4797,6 +4977,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049007</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4923,6 +5108,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049009</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5049,6 +5239,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049017</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5175,6 +5370,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049019</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5301,6 +5501,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049021</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5408,6 +5613,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048996</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5534,6 +5744,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049018</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5646,6 +5861,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525973</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5758,6 +5978,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528299</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5873,6 +6098,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034749</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5988,6 +6218,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034753</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6103,6 +6338,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034769</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6218,6 +6458,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048970</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6333,6 +6578,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048971</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6448,6 +6698,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048986</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6563,6 +6818,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048995</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6678,6 +6938,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6793,6 +7058,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049030</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6908,6 +7178,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049035</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7023,6 +7298,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095205</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7135,6 +7415,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119523535</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7247,6 +7532,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525839</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7359,6 +7649,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525856</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7471,6 +7766,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526277</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7591,6 +7891,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048966</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7705,6 +8010,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048968</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7832,6 +8142,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048981</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7964,6 +8279,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048983</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8084,6 +8404,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049001</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8204,6 +8529,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049028</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8324,6 +8654,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049033</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8439,6 +8774,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048974</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8571,6 +8911,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049022</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8707,6 +9052,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049032</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8823,6 +9173,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135005878</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8939,6 +9294,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009801</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9063,6 +9423,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034742</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9187,6 +9552,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048989</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9311,6 +9681,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049031</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9435,6 +9810,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095195</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9559,6 +9939,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095196</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9683,6 +10068,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095211</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9790,6 +10180,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525652</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9906,6 +10301,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135002845</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10022,6 +10422,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135006904</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10146,6 +10551,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034747</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10270,6 +10680,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034758</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10394,6 +10809,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034761</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10518,6 +10938,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034765</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10630,6 +11055,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048975</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10754,6 +11184,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049002</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10878,6 +11313,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049003</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11002,6 +11442,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049023</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11126,6 +11571,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049026</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11250,6 +11700,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049038</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11374,6 +11829,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095199</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11498,6 +11958,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095202</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11622,6 +12087,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095204</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11746,6 +12216,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095206</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11870,6 +12345,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095208</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11994,6 +12474,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095210</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12118,6 +12603,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095207</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12242,6 +12732,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095215</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12353,6 +12848,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525443</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12477,6 +12977,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048978</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12601,6 +13106,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048982</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12708,6 +13218,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526344</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12824,6 +13339,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135005564</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12940,6 +13460,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135006022</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13043,6 +13568,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034766</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13150,6 +13680,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034738</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13257,6 +13792,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034739</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13364,6 +13904,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034740</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13471,6 +14016,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034750</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13578,6 +14128,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034771</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13685,6 +14240,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048973</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13792,6 +14352,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048987</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13899,6 +14464,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049020</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14006,6 +14576,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049037</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14113,6 +14688,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095209</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14220,6 +14800,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095212</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14327,6 +14912,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095214</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14443,6 +15033,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095219</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14550,6 +15145,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526215</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14666,6 +15266,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135005577</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14782,6 +15387,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135006961</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14898,6 +15508,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009659</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15014,6 +15629,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009818</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15138,6 +15758,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034755</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15262,6 +15887,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034763</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15386,6 +16016,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048998</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15510,6 +16145,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095194</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15634,6 +16274,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095213</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15758,6 +16403,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095221</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15865,6 +16515,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525842</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15972,6 +16627,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119525850</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16083,6 +16743,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135002295</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16199,6 +16864,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034744</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16315,6 +16985,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034752</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16427,6 +17102,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048992</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16539,6 +17219,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049013</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16646,6 +17331,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049016</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16762,6 +17452,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034745</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16878,6 +17573,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034757</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16990,6 +17690,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049012</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17114,6 +17819,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034746</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17238,6 +17948,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034759</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17362,6 +18077,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034768</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17469,6 +18189,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048985</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17576,6 +18301,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048993</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17700,6 +18430,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049010</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17824,6 +18559,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095201</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17948,8 +18688,163 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135095203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135048972</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135049008</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135049024</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135034751</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135034756</v>
       </c>
       <c r="B7" t="n">
-        <v>91985</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135049006</v>
       </c>
       <c r="B8" t="n">
-        <v>91985</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>135049029</v>
       </c>
       <c r="B9" t="n">
-        <v>91958</v>
+        <v>92000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>135034737</v>
       </c>
       <c r="B10" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135048969</v>
       </c>
       <c r="B11" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>135095197</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>135095200</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135095218</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>135034733</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>135034734</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>135034735</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>135048979</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>135049004</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135049036</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>135095216</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>135095217</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>135048999</v>
       </c>
       <c r="B24" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>135049015</v>
       </c>
       <c r="B25" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135049034</v>
       </c>
       <c r="B26" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135048976</v>
       </c>
       <c r="B27" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135048977</v>
       </c>
       <c r="B28" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>135048980</v>
       </c>
       <c r="B29" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>135048984</v>
       </c>
       <c r="B30" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>135048988</v>
       </c>
       <c r="B31" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>135048990</v>
       </c>
       <c r="B32" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>135048991</v>
       </c>
       <c r="B33" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135048994</v>
       </c>
       <c r="B34" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>135048997</v>
       </c>
       <c r="B35" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>135049000</v>
       </c>
       <c r="B36" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135049007</v>
       </c>
       <c r="B37" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>135049009</v>
       </c>
       <c r="B38" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135049017</v>
       </c>
       <c r="B39" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135049019</v>
       </c>
       <c r="B40" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>135049021</v>
       </c>
       <c r="B41" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>135048996</v>
       </c>
       <c r="B42" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135049018</v>
       </c>
       <c r="B43" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>135034749</v>
       </c>
       <c r="B46" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>135034753</v>
       </c>
       <c r="B47" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>135034769</v>
       </c>
       <c r="B48" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135048970</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135048971</v>
       </c>
       <c r="B50" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135048986</v>
       </c>
       <c r="B51" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>135048995</v>
       </c>
       <c r="B52" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>135049025</v>
       </c>
       <c r="B53" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>135049030</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135049035</v>
       </c>
       <c r="B55" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135095205</v>
       </c>
       <c r="B56" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>135048966</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>135048968</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>135048981</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135048983</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135049001</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135049028</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135049033</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>135048974</v>
       </c>
       <c r="B68" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>135049022</v>
       </c>
       <c r="B69" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>135049032</v>
       </c>
       <c r="B70" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>135005878</v>
       </c>
       <c r="B71" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135009801</v>
       </c>
       <c r="B72" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135034742</v>
       </c>
       <c r="B73" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>135048989</v>
       </c>
       <c r="B74" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>135049031</v>
       </c>
       <c r="B75" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>135095195</v>
       </c>
       <c r="B76" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>135095196</v>
       </c>
       <c r="B77" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>135095211</v>
       </c>
       <c r="B78" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>135002845</v>
       </c>
       <c r="B80" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135006904</v>
       </c>
       <c r="B81" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>135034747</v>
       </c>
       <c r="B82" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>135034758</v>
       </c>
       <c r="B83" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>135034761</v>
       </c>
       <c r="B84" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>135034765</v>
       </c>
       <c r="B85" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135048975</v>
       </c>
       <c r="B86" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>135049002</v>
       </c>
       <c r="B87" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>135049003</v>
       </c>
       <c r="B88" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>135049023</v>
       </c>
       <c r="B89" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>135049026</v>
       </c>
       <c r="B90" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>135049038</v>
       </c>
       <c r="B91" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>135095199</v>
       </c>
       <c r="B92" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>135095202</v>
       </c>
       <c r="B93" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>135095204</v>
       </c>
       <c r="B94" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>135095206</v>
       </c>
       <c r="B95" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>135095208</v>
       </c>
       <c r="B96" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>135095210</v>
       </c>
       <c r="B97" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>135095207</v>
       </c>
       <c r="B98" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>135095215</v>
       </c>
       <c r="B99" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>135048978</v>
       </c>
       <c r="B101" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>135048982</v>
       </c>
       <c r="B102" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>135005564</v>
       </c>
       <c r="B104" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>135006022</v>
       </c>
       <c r="B105" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>135034766</v>
       </c>
       <c r="B106" t="n">
-        <v>98054</v>
+        <v>98098</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>135034738</v>
       </c>
       <c r="B107" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>135034739</v>
       </c>
       <c r="B108" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>135034740</v>
       </c>
       <c r="B109" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>135034750</v>
       </c>
       <c r="B110" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>135034771</v>
       </c>
       <c r="B111" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>135048973</v>
       </c>
       <c r="B112" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>135048987</v>
       </c>
       <c r="B113" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>135049020</v>
       </c>
       <c r="B114" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>135049037</v>
       </c>
       <c r="B115" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>135095209</v>
       </c>
       <c r="B116" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>135095212</v>
       </c>
       <c r="B117" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>135095214</v>
       </c>
       <c r="B118" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>135095219</v>
       </c>
       <c r="B119" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>135005577</v>
       </c>
       <c r="B121" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>135006961</v>
       </c>
       <c r="B122" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>135009659</v>
       </c>
       <c r="B123" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>135009818</v>
       </c>
       <c r="B124" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>135034755</v>
       </c>
       <c r="B125" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>135034763</v>
       </c>
       <c r="B126" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135048998</v>
       </c>
       <c r="B127" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>135095194</v>
       </c>
       <c r="B128" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>135095213</v>
       </c>
       <c r="B129" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>135095221</v>
       </c>
       <c r="B130" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>135002295</v>
       </c>
       <c r="B133" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>135034744</v>
       </c>
       <c r="B134" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>135034752</v>
       </c>
       <c r="B135" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>135048992</v>
       </c>
       <c r="B136" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>135049013</v>
       </c>
       <c r="B137" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>135049016</v>
       </c>
       <c r="B138" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>135034745</v>
       </c>
       <c r="B139" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>135034757</v>
       </c>
       <c r="B140" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>135049012</v>
       </c>
       <c r="B141" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>135034746</v>
       </c>
       <c r="B142" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>135034759</v>
       </c>
       <c r="B143" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>135034768</v>
       </c>
       <c r="B144" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>135048985</v>
       </c>
       <c r="B145" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>135048993</v>
       </c>
       <c r="B146" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>135049010</v>
       </c>
       <c r="B147" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>135095201</v>
       </c>
       <c r="B148" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>135095203</v>
       </c>
       <c r="B149" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 26453-2026 artfynd.xlsx
+++ b/artfynd/A 26453-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135048972</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135049008</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135049024</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135034751</v>
       </c>
       <c r="B6" t="n">
-        <v>92027</v>
+        <v>92054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135034756</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135049006</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>135049029</v>
       </c>
       <c r="B9" t="n">
-        <v>92000</v>
+        <v>92027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>135034737</v>
       </c>
       <c r="B10" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135048969</v>
       </c>
       <c r="B11" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>135095197</v>
       </c>
       <c r="B12" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>135095200</v>
       </c>
       <c r="B13" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135095218</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>135034733</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>135034734</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>135034735</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>135048979</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>135049004</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135049036</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>135095216</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>135095217</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>135048999</v>
       </c>
       <c r="B24" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>135049015</v>
       </c>
       <c r="B25" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135049034</v>
       </c>
       <c r="B26" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135048976</v>
       </c>
       <c r="B27" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135048977</v>
       </c>
       <c r="B28" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>135048980</v>
       </c>
       <c r="B29" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>135048984</v>
       </c>
       <c r="B30" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>135048988</v>
       </c>
       <c r="B31" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>135048990</v>
       </c>
       <c r="B32" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>135048991</v>
       </c>
       <c r="B33" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135048994</v>
       </c>
       <c r="B34" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>135048997</v>
       </c>
       <c r="B35" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>135049000</v>
       </c>
       <c r="B36" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135049007</v>
       </c>
       <c r="B37" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>135049009</v>
       </c>
       <c r="B38" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135049017</v>
       </c>
       <c r="B39" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135049019</v>
       </c>
       <c r="B40" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>135049021</v>
       </c>
       <c r="B41" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>135048996</v>
       </c>
       <c r="B42" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135049018</v>
       </c>
       <c r="B43" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>135005878</v>
       </c>
       <c r="B71" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135009801</v>
       </c>
       <c r="B72" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135034742</v>
       </c>
       <c r="B73" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>135048989</v>
       </c>
       <c r="B74" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>135049031</v>
       </c>
       <c r="B75" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>135095195</v>
       </c>
       <c r="B76" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>135095196</v>
       </c>
       <c r="B77" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>135095211</v>
       </c>
       <c r="B78" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>135002845</v>
       </c>
       <c r="B80" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135006904</v>
       </c>
       <c r="B81" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>135034747</v>
       </c>
       <c r="B82" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>135034758</v>
       </c>
       <c r="B83" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>135034761</v>
       </c>
       <c r="B84" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>135034765</v>
       </c>
       <c r="B85" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135048975</v>
       </c>
       <c r="B86" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>135049002</v>
       </c>
       <c r="B87" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>135049003</v>
       </c>
       <c r="B88" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>135049023</v>
       </c>
       <c r="B89" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>135049026</v>
       </c>
       <c r="B90" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>135049038</v>
       </c>
       <c r="B91" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>135095199</v>
       </c>
       <c r="B92" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>135095202</v>
       </c>
       <c r="B93" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>135095204</v>
       </c>
       <c r="B94" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>135095206</v>
       </c>
       <c r="B95" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>135095208</v>
       </c>
       <c r="B96" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>135095210</v>
       </c>
       <c r="B97" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>135095207</v>
       </c>
       <c r="B98" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>135095215</v>
       </c>
       <c r="B99" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>135048978</v>
       </c>
       <c r="B101" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>135048982</v>
       </c>
       <c r="B102" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>135005564</v>
       </c>
       <c r="B104" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>135006022</v>
       </c>
       <c r="B105" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>135034766</v>
       </c>
       <c r="B106" t="n">
-        <v>98098</v>
+        <v>98125</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>135034738</v>
       </c>
       <c r="B107" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>135034739</v>
       </c>
       <c r="B108" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>135034740</v>
       </c>
       <c r="B109" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>135034750</v>
       </c>
       <c r="B110" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>135034771</v>
       </c>
       <c r="B111" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>135048973</v>
       </c>
       <c r="B112" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>135048987</v>
       </c>
       <c r="B113" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>135049020</v>
       </c>
       <c r="B114" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>135049037</v>
       </c>
       <c r="B115" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>135095209</v>
       </c>
       <c r="B116" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>135095212</v>
       </c>
       <c r="B117" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>135095214</v>
       </c>
       <c r="B118" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>135095219</v>
       </c>
       <c r="B119" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>135005577</v>
       </c>
       <c r="B121" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>135006961</v>
       </c>
       <c r="B122" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>135009659</v>
       </c>
       <c r="B123" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>135009818</v>
       </c>
       <c r="B124" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>135034755</v>
       </c>
       <c r="B125" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>135034763</v>
       </c>
       <c r="B126" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135048998</v>
       </c>
       <c r="B127" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>135095194</v>
       </c>
       <c r="B128" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>135095213</v>
       </c>
       <c r="B129" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>135095221</v>
       </c>
       <c r="B130" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>135002295</v>
       </c>
       <c r="B133" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>135034744</v>
       </c>
       <c r="B134" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>135034752</v>
       </c>
       <c r="B135" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>135048992</v>
       </c>
       <c r="B136" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>135049013</v>
       </c>
       <c r="B137" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>135049016</v>
       </c>
       <c r="B138" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>135034745</v>
       </c>
       <c r="B139" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>135034757</v>
       </c>
       <c r="B140" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>135049012</v>
       </c>
       <c r="B141" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>135034746</v>
       </c>
       <c r="B142" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>135034759</v>
       </c>
       <c r="B143" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>135034768</v>
       </c>
       <c r="B144" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>135048985</v>
       </c>
       <c r="B145" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>135048993</v>
       </c>
       <c r="B146" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>135049010</v>
       </c>
       <c r="B147" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>135095201</v>
       </c>
       <c r="B148" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>135095203</v>
       </c>
       <c r="B149" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
